--- a/04_DESIGN_TABLES/DesignTable_0318_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_0318_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="C2" t="n">
         <v>0.50807</v>
@@ -563,7 +563,7 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.117</v>
+        <v>0.127</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -597,12 +597,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L35 = 0.85 (table had 0.84) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 0.850 (+/-.020) / hex 0.8750 vs Air-Way 0.84 / 0.88: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.84 -&gt; OMi 0.85 (Items!L35, M013) | MS51531D L1 0.850 (+/-.020) / hex 0.8750 vs Air-Way 0.85 / 0.88: AGREE</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="C3" t="n">
         <v>0.21939</v>
@@ -651,7 +651,7 @@
         <v>0.179</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -685,12 +685,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L30 = 0.55 (table had 0.54) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 0.550 (+/-.020) / hex 0.3750 vs Air-Way 0.54 / 0.38: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.54 -&gt; OMi 0.55 (Items!L30, M013) | MS51531D L1 0.550 (+/-.020) / hex 0.3750 vs Air-Way 0.55 / 0.38: AGREE</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="C4" t="n">
         <v>0.25403</v>
@@ -739,7 +739,7 @@
         <v>0.241</v>
       </c>
       <c r="M4" t="n">
-        <v>0.094</v>
+        <v>0.104</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -773,12 +773,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L31 = 0.61 (table had 0.6) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 0.610 (+/-.020) / hex 0.4375 vs Air-Way 0.6 / 0.44: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.6 -&gt; OMi 0.61 (Items!L31, M013) | MS51531D L1 0.610 (+/-.020) / hex 0.4375 vs Air-Way 0.61 / 0.44: AGREE</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="C5" t="n">
         <v>0.32332</v>
@@ -827,7 +827,7 @@
         <v>0.304</v>
       </c>
       <c r="M5" t="n">
-        <v>0.078</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -861,12 +861,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L32 = 0.62 (table had 0.61) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 0.620 (+/-.020) / hex 0.5625 vs Air-Way 0.61 / 0.56: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.61 -&gt; OMi 0.62 (Items!L32, M013) | MS51531D L1 0.620 (+/-.020) / hex 0.5625 vs Air-Way 0.62 / 0.56: AGREE</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="C6" t="n">
         <v>0.36373</v>
@@ -915,7 +915,7 @@
         <v>0.373</v>
       </c>
       <c r="M6" t="n">
-        <v>0.091</v>
+        <v>0.101</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L33 = 0.68 (table had 0.67) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 0.680 (+/-.020) / hex 0.6250 vs Air-Way 0.67 / 0.63: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.67 -&gt; OMi 0.68 (Items!L33, M013) | MS51531D L1 0.680 (+/-.020) / hex 0.6250 vs Air-Way 0.68 / 0.63: AGREE</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="C7" t="n">
         <v>0.39837</v>
@@ -1003,7 +1003,7 @@
         <v>0.439</v>
       </c>
       <c r="M7" t="n">
-        <v>0.117</v>
+        <v>0.127</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L34 = 0.73 (table had 0.72) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 0.730 (+/-.020) / hex 0.6875 vs Air-Way 0.72 / 0.69: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.72 -&gt; OMi 0.73 (Items!L34, M013) | MS51531D L1 0.730 (+/-.020) / hex 0.6875 vs Air-Way 0.73 / 0.69: AGREE</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="C8" t="n">
         <v>0.57735</v>
@@ -1091,7 +1091,7 @@
         <v>0.696</v>
       </c>
       <c r="M8" t="n">
-        <v>0.153</v>
+        <v>0.163</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L36 = 0.98 (table had 0.97) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 0.980 (+/-.020) / hex 1.0000 vs Air-Way 0.97 / 1: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.97 -&gt; OMi 0.98 (Items!L36, M013) | MS51531D L1 0.980 (+/-.020) / hex 1.0000 vs Air-Way 0.98 / 1: AGREE</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="C9" t="n">
         <v>0.7216900000000001</v>
@@ -1179,7 +1179,7 @@
         <v>0.832</v>
       </c>
       <c r="M9" t="n">
-        <v>0.152</v>
+        <v>0.162</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L37 = 1.03 (table had 1.02) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 1.030 (+/-.020) / hex 1.2500 vs Air-Way 1.02 / 1.25: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.02 -&gt; OMi 1.03 (Items!L37, M013) | MS51531D L1 1.030 (+/-.020) / hex 1.2500 vs Air-Way 1.03 / 1.25: AGREE</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="C10" t="n">
         <v>0.86603</v>
@@ -1267,7 +1267,7 @@
         <v>1.087</v>
       </c>
       <c r="M10" t="n">
-        <v>0.158</v>
+        <v>0.168</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L38 = 1.13 (table had 1.12) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 1.130 (+/-.020) / hex 1.5000 vs Air-Way 1.12 / 1.5: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.12 -&gt; OMi 1.13 (Items!L38, M013) | MS51531D L1 1.130 (+/-.020) / hex 1.5000 vs Air-Way 1.13 / 1.5: AGREE</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="C11" t="n">
         <v>1.1547</v>
@@ -1355,7 +1355,7 @@
         <v>1.344</v>
       </c>
       <c r="M11" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L39 = 1.23 (table had 1.22) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 1.230 (+/-.020) / hex 2.0000 vs Air-Way 1.22 / 2: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.22 -&gt; OMi 1.23 (Items!L39, M013) | MS51531D L1 1.230 (+/-.020) / hex 2.0000 vs Air-Way 1.23 / 2: AGREE</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 1.420 (+/-.020) / hex 2.2500 vs Air-Way 1.42 / 2.25: AGREE</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on CHEX@HEX=2.25~2.25 | MS51531D L1 1.420 (+/-.020) / hex 2.2500 vs Air-Way 1.42 / 2.25: AGREE</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="C13" t="n">
         <v>1.66277</v>
@@ -1531,7 +1531,7 @@
         <v>2.164</v>
       </c>
       <c r="M13" t="n">
-        <v>0.278</v>
+        <v>0.288</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L41 = 1.75 (table had 1.74) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | MS51531D L1 1.750 (+/-.020) / hex 2.8750 vs Air-Way 1.74 / 2.88: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.74 -&gt; OMi 1.75 (Items!L41, M013) | MS51531D L1 1.750 (+/-.020) / hex 2.8750 vs Air-Way 1.75 / 2.88: AGREE</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_0318_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_0318_SW2.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="C2" t="n">
         <v>0.50807</v>
@@ -563,7 +563,7 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.127</v>
+        <v>0.117</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -597,12 +597,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L35 = 0.85 (table had 0.84) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L35 = 0.85 (table had 0.84) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 0.84 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.85) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.84 -&gt; OMi 0.85 (Items!L35, M013) | MS51531D L1 0.850 (+/-.020) / hex 0.8750 vs Air-Way 0.85 / 0.88: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.84 -&gt; OMi 0.85 (Items!L35, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 0.85 -&gt; Air-Way 0.84 | MS51531D L1 0.850 (+/-.020) / hex 0.8750 vs Air-Way 0.84 / 0.88: AGREE</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="C3" t="n">
         <v>0.21939</v>
@@ -651,7 +651,7 @@
         <v>0.179</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -685,12 +685,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L30 = 0.55 (table had 0.54) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L30 = 0.55 (table had 0.54) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 0.54 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.55) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.54 -&gt; OMi 0.55 (Items!L30, M013) | MS51531D L1 0.550 (+/-.020) / hex 0.3750 vs Air-Way 0.55 / 0.38: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.54 -&gt; OMi 0.55 (Items!L30, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 0.55 -&gt; Air-Way 0.54 | MS51531D L1 0.550 (+/-.020) / hex 0.3750 vs Air-Way 0.54 / 0.38: AGREE</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="C4" t="n">
         <v>0.25403</v>
@@ -739,7 +739,7 @@
         <v>0.241</v>
       </c>
       <c r="M4" t="n">
-        <v>0.104</v>
+        <v>0.094</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -773,12 +773,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L31 = 0.61 (table had 0.6) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L31 = 0.61 (table had 0.6) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 0.6 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.61) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.6 -&gt; OMi 0.61 (Items!L31, M013) | MS51531D L1 0.610 (+/-.020) / hex 0.4375 vs Air-Way 0.61 / 0.44: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.6 -&gt; OMi 0.61 (Items!L31, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 0.61 -&gt; Air-Way 0.6 | MS51531D L1 0.610 (+/-.020) / hex 0.4375 vs Air-Way 0.6 / 0.44: AGREE</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="C5" t="n">
         <v>0.32332</v>
@@ -827,7 +827,7 @@
         <v>0.304</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -861,12 +861,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L32 = 0.62 (table had 0.61) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L32 = 0.62 (table had 0.61) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 0.61 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.62) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.61 -&gt; OMi 0.62 (Items!L32, M013) | MS51531D L1 0.620 (+/-.020) / hex 0.5625 vs Air-Way 0.62 / 0.56: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.61 -&gt; OMi 0.62 (Items!L32, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 0.62 -&gt; Air-Way 0.61 | MS51531D L1 0.620 (+/-.020) / hex 0.5625 vs Air-Way 0.61 / 0.56: AGREE</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="C6" t="n">
         <v>0.36373</v>
@@ -915,7 +915,7 @@
         <v>0.373</v>
       </c>
       <c r="M6" t="n">
-        <v>0.101</v>
+        <v>0.091</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L33 = 0.68 (table had 0.67) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L33 = 0.68 (table had 0.67) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 0.67 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.68) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.67 -&gt; OMi 0.68 (Items!L33, M013) | MS51531D L1 0.680 (+/-.020) / hex 0.6250 vs Air-Way 0.68 / 0.63: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.67 -&gt; OMi 0.68 (Items!L33, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 0.68 -&gt; Air-Way 0.67 | MS51531D L1 0.680 (+/-.020) / hex 0.6250 vs Air-Way 0.67 / 0.63: AGREE</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="C7" t="n">
         <v>0.39837</v>
@@ -1003,7 +1003,7 @@
         <v>0.439</v>
       </c>
       <c r="M7" t="n">
-        <v>0.127</v>
+        <v>0.117</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L34 = 0.73 (table had 0.72) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L34 = 0.73 (table had 0.72) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 0.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.73) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.72 -&gt; OMi 0.73 (Items!L34, M013) | MS51531D L1 0.730 (+/-.020) / hex 0.6875 vs Air-Way 0.73 / 0.69: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.72 -&gt; OMi 0.73 (Items!L34, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 0.73 -&gt; Air-Way 0.72 | MS51531D L1 0.730 (+/-.020) / hex 0.6875 vs Air-Way 0.72 / 0.69: AGREE</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="C8" t="n">
         <v>0.57735</v>
@@ -1091,7 +1091,7 @@
         <v>0.696</v>
       </c>
       <c r="M8" t="n">
-        <v>0.163</v>
+        <v>0.153</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L36 = 0.98 (table had 0.97) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L36 = 0.98 (table had 0.97) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 0.97 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.98) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.97 -&gt; OMi 0.98 (Items!L36, M013) | MS51531D L1 0.980 (+/-.020) / hex 1.0000 vs Air-Way 0.98 / 1: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 0.97 -&gt; OMi 0.98 (Items!L36, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 0.98 -&gt; Air-Way 0.97 | MS51531D L1 0.980 (+/-.020) / hex 1.0000 vs Air-Way 0.97 / 1: AGREE</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="C9" t="n">
         <v>0.7216900000000001</v>
@@ -1179,7 +1179,7 @@
         <v>0.832</v>
       </c>
       <c r="M9" t="n">
-        <v>0.162</v>
+        <v>0.152</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L37 = 1.03 (table had 1.02) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L37 = 1.03 (table had 1.02) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 1.02 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.03) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.02 -&gt; OMi 1.03 (Items!L37, M013) | MS51531D L1 1.030 (+/-.020) / hex 1.2500 vs Air-Way 1.03 / 1.25: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.02 -&gt; OMi 1.03 (Items!L37, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 1.03 -&gt; Air-Way 1.02 | MS51531D L1 1.030 (+/-.020) / hex 1.2500 vs Air-Way 1.02 / 1.25: AGREE</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="C10" t="n">
         <v>0.86603</v>
@@ -1267,7 +1267,7 @@
         <v>1.087</v>
       </c>
       <c r="M10" t="n">
-        <v>0.168</v>
+        <v>0.158</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L38 = 1.13 (table had 1.12) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L38 = 1.13 (table had 1.12) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 1.12 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.13) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.12 -&gt; OMi 1.13 (Items!L38, M013) | MS51531D L1 1.130 (+/-.020) / hex 1.5000 vs Air-Way 1.13 / 1.5: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.12 -&gt; OMi 1.13 (Items!L38, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 1.13 -&gt; Air-Way 1.12 | MS51531D L1 1.130 (+/-.020) / hex 1.5000 vs Air-Way 1.12 / 1.5: AGREE</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="C11" t="n">
         <v>1.1547</v>
@@ -1355,7 +1355,7 @@
         <v>1.344</v>
       </c>
       <c r="M11" t="n">
-        <v>0.213</v>
+        <v>0.203</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L39 = 1.23 (table had 1.22) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L39 = 1.23 (table had 1.22) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 1.22 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.23) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.22 -&gt; OMi 1.23 (Items!L39, M013) | MS51531D L1 1.230 (+/-.020) / hex 2.0000 vs Air-Way 1.23 / 2: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.22 -&gt; OMi 1.23 (Items!L39, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 1.23 -&gt; Air-Way 1.22 | MS51531D L1 1.230 (+/-.020) / hex 2.0000 vs Air-Way 1.22 / 2: AGREE</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="C13" t="n">
         <v>1.66277</v>
@@ -1531,7 +1531,7 @@
         <v>2.164</v>
       </c>
       <c r="M13" t="n">
-        <v>0.288</v>
+        <v>0.278</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L41 = 1.75 (table had 1.74) [user 2026-10-18 A19] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
+          <t>Air-Way s47 only (double-pass 13 rows); Air-Way part numbers printed as 318-n; config names zero-padded to 0318-nn; L1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L41 = 1.75 (table had 1.74) [user 2026-10-18 A19]; L1@DRIVE: Air-Way 1.74 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.75) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: L1 / hex / thread: Air-Way; internal: MS51531D (Nut, Tube Coupling, 37 Degree Flared) - tube bore D1, internal shoulder at I1 from the thread face, thread length J1 (full thread min); thread pocket = ASME B1.1 basic minor diameter (D - 1.082532P), helical 60deg thread from the minor to the basic major (no taper); Brennan 0318-08 STEP: shoulder at 0.723 = I1, bore 0.568 = D1, L 0.850 (VERIFIED -08 only); hex over the full length, 30deg end chamfers and the 45deg thread countersink NOT modelled; no internal flare cone (none on MS51531D or the Brennan STEP)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.74 -&gt; OMi 1.75 (Items!L41, M013) | MS51531D L1 1.750 (+/-.020) / hex 2.8750 vs Air-Way 1.75 / 2.88: AGREE</t>
+          <t>A19 (user 2026-10-18, group 3 open): L1@DRIVE 1.74 -&gt; OMi 1.75 (Items!L41, M013) | 2026-10-20 Air-Way first: L1@DRIVE OMi/Brennan 1.75 -&gt; Air-Way 1.74 | MS51531D L1 1.750 (+/-.020) / hex 2.8750 vs Air-Way 1.74 / 2.88: AGREE</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
